--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="117">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,9 +270,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée représente la pertinence d'un lot de soumission. </t>
-  </si>
-  <si>
     <t>Cette métadonnée représente la pertinence d'un lot de soumission.</t>
   </si>
   <si>
@@ -302,16 +299,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Titre du lot de soumission </t>
-  </si>
-  <si>
     <t>Titre du lot de soumission</t>
   </si>
   <si>
     <t>xdm-submission-set.comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cette métadonnée contient le commentaire associé au lot de soumission. </t>
   </si>
   <si>
     <t>Cette métadonnée contient le commentaire associé au lot de soumission.</t>
@@ -350,7 +341,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Ensemble de métadonnées représentant le type d’activité associé à l’événement clinique ayant abouti à la constitution du lot de soumission. </t>
+    <t>Ensemble de métadonnées représentant le type d’activité associé à l’événement clinique ayant abouti à la constitution du lot de soumission.</t>
   </si>
   <si>
     <t>**Submission Set**</t>
@@ -1067,7 +1058,7 @@
         <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1082,23 +1073,23 @@
         <v>73</v>
       </c>
       <c r="T4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U4" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V4" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W4" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X4" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="U4" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V4" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W4" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X4" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>73</v>
@@ -1133,10 +1124,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1159,13 +1150,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1216,7 +1207,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -1233,10 +1224,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1259,13 +1250,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1316,7 +1307,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1333,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1359,13 +1350,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1416,7 +1407,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1433,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1459,13 +1450,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1516,7 +1507,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -1533,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1559,13 +1550,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1616,7 +1607,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -1633,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1659,13 +1650,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1716,7 +1707,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -1733,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1759,13 +1750,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1792,11 +1783,11 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -1814,7 +1805,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -1831,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1857,13 +1848,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1914,7 +1905,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1957,13 +1948,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2014,7 +2005,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2031,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2057,13 +2048,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2114,7 +2105,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>

--- a/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
